--- a/data/dividends_info_20260612.xlsx
+++ b/data/dividends_info_20260612.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>66.08000183105469</v>
+        <v>67.75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1361985434414803</v>
+        <v>0.1328413284132841</v>
       </c>
       <c r="J2" t="n">
         <v>276</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>59.84999847412109</v>
+        <v>60.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.16959067309363</v>
+        <v>1.149425258556917</v>
       </c>
       <c r="J3" t="n">
         <v>255</v>
@@ -585,11 +585,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06</v>
+        <v>0.004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -613,14 +613,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0004587470</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.100000381469727</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.8333333519597853</v>
       </c>
       <c r="J4" t="n">
         <v>185</v>
@@ -632,15 +632,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004</v>
+        <v>0.09</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -660,14 +660,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IT0004587470</t>
+          <t>NL0000226223</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4799999892711639</v>
+        <v>67.75</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8333333519597853</v>
+        <v>0.1328413284132841</v>
       </c>
       <c r="J5" t="n">
         <v>185</v>
@@ -679,25 +679,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09</v>
+        <v>0.077</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -707,30 +707,30 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NL0000226223</t>
+          <t>IT0001469383</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>66.08000183105469</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1361985434414803</v>
+        <v>3.68421067761643</v>
       </c>
       <c r="J6" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K6" t="n">
-        <v>187</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.077</v>
+        <v>0.27</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -754,14 +754,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IT0001469383</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.095000028610229</v>
+        <v>23.21999931335449</v>
       </c>
       <c r="I7" t="n">
-        <v>3.675417610904753</v>
+        <v>1.162790732059648</v>
       </c>
       <c r="J7" t="n">
         <v>164</v>
@@ -773,11 +773,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -801,30 +801,30 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0005312027</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.84499931335449</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="I8" t="n">
-        <v>1.181877908143189</v>
+        <v>3.514938453229105</v>
       </c>
       <c r="J8" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K8" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -833,12 +833,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -848,30 +848,30 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IT0005312027</t>
+          <t>IT0005359101</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.71999979019165</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I9" t="n">
-        <v>3.496503624754485</v>
+        <v>0.8108108003614941</v>
       </c>
       <c r="J9" t="n">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="K9" t="n">
-        <v>159</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06</v>
+        <v>0.004</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -895,14 +895,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IT0005359101</t>
+          <t>IT0004587470</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.400000095367432</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8108108003614941</v>
+        <v>0.8333333519597853</v>
       </c>
       <c r="J10" t="n">
         <v>129</v>
@@ -914,11 +914,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.004</v>
+        <v>0.05</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -927,45 +927,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>IT0004587470</t>
+          <t>IT0005531238</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4799999892711639</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8333333519597853</v>
+        <v>0.8650518717136495</v>
       </c>
       <c r="J11" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="K11" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05</v>
+        <v>0.038</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -974,45 +974,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>IT0005531238</t>
+          <t>IT0005187460</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.539999961853027</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I12" t="n">
-        <v>0.902527082026837</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J12" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="K12" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.038</v>
+        <v>0.27</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1036,30 +1036,30 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IT0005187460</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>23.21999931335449</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>1.162790732059648</v>
       </c>
       <c r="J13" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="K13" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1068,59 +1068,59 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0005573818</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.85000038146973</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I14" t="n">
-        <v>1.181619236290942</v>
+        <v>5.067567502259338</v>
       </c>
       <c r="J14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K14" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09</v>
+        <v>0.038</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1130,30 +1130,30 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NL0000226223</t>
+          <t>IT0005187460</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>66.08000183105469</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1361985434414803</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J15" t="n">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="K15" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1177,30 +1177,30 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>IT0005573818</t>
+          <t>IT0004098510</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.960000038146973</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I16" t="n">
-        <v>5.03355701476259</v>
+        <v>4.098360719811497</v>
       </c>
       <c r="J16" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="K16" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.004</v>
+        <v>0.14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1209,45 +1209,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>IT0004587470</t>
+          <t>IT0005285942</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4799999892711639</v>
+        <v>4.289999961853027</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8333333519597853</v>
+        <v>3.263403292421668</v>
       </c>
       <c r="J17" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="K17" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.038</v>
+        <v>0.26</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1256,45 +1256,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>IT0005187460</t>
+          <t>IT0003128367</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.980000019073486</v>
+        <v>9.793999671936035</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7630522059128382</v>
+        <v>2.654686631703801</v>
       </c>
       <c r="J18" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K18" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1318,30 +1318,30 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>IT0004098510</t>
+          <t>IT0005221517</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6.050000190734863</v>
+        <v>14.23999977111816</v>
       </c>
       <c r="I19" t="n">
-        <v>4.132231274684204</v>
+        <v>4.213483213791417</v>
       </c>
       <c r="J19" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="K19" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1365,14 +1365,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IT0005285942</t>
+          <t>NL0015001OJ9</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.179999828338623</v>
+        <v>3.703999996185303</v>
       </c>
       <c r="I20" t="n">
-        <v>3.349282434196755</v>
+        <v>5.939524844129992</v>
       </c>
       <c r="J20" t="n">
         <v>38</v>
@@ -1384,11 +1384,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1407,19 +1407,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IT0003128367</t>
+          <t>IT0005278236</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.793000221252441</v>
+        <v>6.304999828338623</v>
       </c>
       <c r="I21" t="n">
-        <v>2.654957562808553</v>
+        <v>1.586042866338192</v>
       </c>
       <c r="J21" t="n">
         <v>38</v>
@@ -1431,11 +1431,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6</v>
+        <v>0.376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1459,14 +1459,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IT0005221517</t>
+          <t>IT0000214293</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.38000011444092</v>
+        <v>18.64999961853027</v>
       </c>
       <c r="I22" t="n">
-        <v>4.17246171922807</v>
+        <v>2.016085832122022</v>
       </c>
       <c r="J22" t="n">
         <v>38</v>
@@ -1478,11 +1478,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1506,30 +1506,30 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NL0015001OJ9</t>
+          <t>IT0004053440</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.706000089645386</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I23" t="n">
-        <v>5.936319338326055</v>
+        <v>2.061855609288493</v>
       </c>
       <c r="J23" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K23" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.004</v>
+        <v>0.05</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1538,45 +1538,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IT0004587470</t>
+          <t>IT0005605701</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.4799999892711639</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8333333519597853</v>
+        <v>0.5494505264177207</v>
       </c>
       <c r="J24" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K24" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1585,45 +1585,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IT0005278236</t>
+          <t>IT0005425365</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.340000152587891</v>
+        <v>2.740000009536743</v>
       </c>
       <c r="I25" t="n">
-        <v>1.577287028284716</v>
+        <v>5.474452535690348</v>
       </c>
       <c r="J25" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K25" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.376</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1647,30 +1647,30 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IT0000214293</t>
+          <t>IT0001382024</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.54999923706055</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I26" t="n">
-        <v>2.026954261263794</v>
+        <v>3.935185028814982</v>
       </c>
       <c r="J26" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1694,30 +1694,30 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>IT0004053440</t>
+          <t>IT0005561441</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.829999923706055</v>
+        <v>4.860000133514404</v>
       </c>
       <c r="I27" t="n">
-        <v>2.058319066387184</v>
+        <v>1.440329178538129</v>
       </c>
       <c r="J27" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K27" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1741,30 +1741,30 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>IT0005605701</t>
+          <t>IT0004195308</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.100000381469727</v>
+        <v>35.29999923706055</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5494505264177207</v>
+        <v>0.4249291876542561</v>
       </c>
       <c r="J28" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K28" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1788,30 +1788,30 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>IT0005425365</t>
+          <t>IT0005508574</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.740000009536743</v>
+        <v>5.150000095367432</v>
       </c>
       <c r="I29" t="n">
-        <v>5.474452535690348</v>
+        <v>0.7766990147433418</v>
       </c>
       <c r="J29" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K29" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1820,45 +1820,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>IT0001382024</t>
+          <t>IT0001207098</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.160000085830688</v>
+        <v>22.6200008392334</v>
       </c>
       <c r="I30" t="n">
-        <v>3.935185028814982</v>
+        <v>1.105216581452932</v>
       </c>
       <c r="J30" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.195</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1882,30 +1882,30 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IT0005561441</t>
+          <t>IT0005331019</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.829999923706055</v>
+        <v>29.39999961853027</v>
       </c>
       <c r="I31" t="n">
-        <v>1.449275385211374</v>
+        <v>0.6632653147284231</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.15</v>
+        <v>0.033</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1929,30 +1929,30 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IT0004195308</t>
+          <t>IT0005089476</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>35.15000152587891</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="I32" t="n">
-        <v>0.426742513480586</v>
+        <v>1.783783760795287</v>
       </c>
       <c r="J32" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04</v>
+        <v>0.29</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1976,30 +1976,30 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IT0005508574</t>
+          <t>IT0005176406</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.050000190734863</v>
+        <v>5.40500020980835</v>
       </c>
       <c r="I33" t="n">
-        <v>0.792079178004532</v>
+        <v>5.365402196909125</v>
       </c>
       <c r="J33" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2018,19 +2018,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IT0001207098</t>
+          <t>IT0001250932</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.78000068664551</v>
+        <v>3.789999961853027</v>
       </c>
       <c r="I34" t="n">
-        <v>1.097453873855936</v>
+        <v>4.221635926396472</v>
       </c>
       <c r="J34" t="n">
         <v>10</v>
@@ -2042,11 +2042,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.195</v>
+        <v>0.1386</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2070,14 +2070,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>IT0005331019</t>
+          <t>IT0003027817</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29.70000076293945</v>
+        <v>2.759999990463257</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6565656396996691</v>
+        <v>5.021739147786607</v>
       </c>
       <c r="J35" t="n">
         <v>10</v>
@@ -2089,11 +2089,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.033</v>
+        <v>0.63</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2117,14 +2117,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>IT0005089476</t>
+          <t>IT0003856405</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.860000014305115</v>
+        <v>53.47999954223633</v>
       </c>
       <c r="I36" t="n">
-        <v>1.774193534741913</v>
+        <v>1.178010481287405</v>
       </c>
       <c r="J36" t="n">
         <v>10</v>
@@ -2136,11 +2136,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2164,14 +2164,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>IT0005176406</t>
+          <t>IT0005043507</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.420000076293945</v>
+        <v>6.400000095367432</v>
       </c>
       <c r="I37" t="n">
-        <v>5.350553430218666</v>
+        <v>2.187499967403711</v>
       </c>
       <c r="J37" t="n">
         <v>10</v>
@@ -2183,11 +2183,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.16</v>
+        <v>0.78</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>IT0001250932</t>
+          <t>IT0005353815</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.793999910354614</v>
+        <v>17.64999961853027</v>
       </c>
       <c r="I38" t="n">
-        <v>4.217185128637635</v>
+        <v>4.419263551604264</v>
       </c>
       <c r="J38" t="n">
         <v>10</v>
@@ -2230,11 +2230,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1386</v>
+        <v>0.85</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2258,14 +2258,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>IT0003027817</t>
+          <t>IT0003796171</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.757999897003174</v>
+        <v>28.22999954223633</v>
       </c>
       <c r="I39" t="n">
-        <v>5.025380898331503</v>
+        <v>3.010981274471054</v>
       </c>
       <c r="J39" t="n">
         <v>10</v>
@@ -2277,11 +2277,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.63</v>
+        <v>0.01</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2305,14 +2305,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>IT0003856405</t>
+          <t>IT0005573123</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>53.90999984741211</v>
+        <v>1.75</v>
       </c>
       <c r="I40" t="n">
-        <v>1.168614360569772</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="J40" t="n">
         <v>10</v>
@@ -2324,11 +2324,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.14</v>
+        <v>0.1813</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2352,14 +2352,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>IT0005043507</t>
+          <t>IT0003153415</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.28000020980835</v>
+        <v>6.432000160217285</v>
       </c>
       <c r="I41" t="n">
-        <v>2.229299288578726</v>
+        <v>2.818718835260031</v>
       </c>
       <c r="J41" t="n">
         <v>10</v>
@@ -2371,11 +2371,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.78</v>
+        <v>0.26</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2399,14 +2399,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>IT0005353815</t>
+          <t>IT0003153621</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18.45000076293945</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I42" t="n">
-        <v>4.227642101602442</v>
+        <v>2.807775308569248</v>
       </c>
       <c r="J42" t="n">
         <v>10</v>
@@ -2418,11 +2418,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.85</v>
+        <v>0.277</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2446,14 +2446,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>IT0003796171</t>
+          <t>IT0003242622</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>27.95000076293945</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="I43" t="n">
-        <v>3.04114481859716</v>
+        <v>2.694552599175406</v>
       </c>
       <c r="J43" t="n">
         <v>10</v>
@@ -2465,58 +2465,58 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.09</v>
+        <v>0.0135</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>NL0000226223</t>
+          <t>IT0004412497</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>66.08000183105469</v>
+        <v>1.059999942779541</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1361985434414803</v>
+        <v>1.273584974410487</v>
       </c>
       <c r="J44" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2540,30 +2540,30 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>IT0005573123</t>
+          <t>IT0005383291</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.679999947547913</v>
+        <v>3.141999959945679</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5952381138223104</v>
+        <v>3.500954850486433</v>
       </c>
       <c r="J45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1813</v>
+        <v>0.024</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2572,12 +2572,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2587,30 +2587,30 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>IT0003153415</t>
+          <t>IT0005670960</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.372000217437744</v>
+        <v>1.919999957084656</v>
       </c>
       <c r="I46" t="n">
-        <v>2.845260417660545</v>
+        <v>1.250000027939678</v>
       </c>
       <c r="J46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2634,30 +2634,30 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>IT0003153621</t>
+          <t>IT0004093263</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.199999809265137</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I47" t="n">
-        <v>2.826087015112318</v>
+        <v>5.26315796078077</v>
       </c>
       <c r="J47" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="K47" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.277</v>
+        <v>0.025</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2681,30 +2681,30 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>IT0003242622</t>
+          <t>IT0005433765</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.23499965667725</v>
+        <v>0.8600000143051147</v>
       </c>
       <c r="I48" t="n">
-        <v>2.706399699967621</v>
+        <v>2.90697669583182</v>
       </c>
       <c r="J48" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="K48" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0135</v>
+        <v>1.11</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2713,45 +2713,45 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>IT0004412497</t>
+          <t>NL0015000K93</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.054999947547913</v>
+        <v>28.04999923706055</v>
       </c>
       <c r="I49" t="n">
-        <v>1.279620916700273</v>
+        <v>3.957219358970367</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="K49" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.11</v>
+        <v>0.6</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2775,30 +2775,30 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>IT0005383291</t>
+          <t>IT0005245508</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.150000095367432</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="I50" t="n">
-        <v>3.492063386339963</v>
+        <v>3.084832783879659</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.024</v>
+        <v>0.2</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2822,30 +2822,30 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>IT0005670960</t>
+          <t>IT0005469264</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.919999957084656</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="I51" t="n">
-        <v>1.250000027939678</v>
+        <v>2.118644161972296</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="K51" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.16</v>
+        <v>0.104</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2869,30 +2869,30 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>IT0004093263</t>
+          <t>IT0001233417</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.009999990463257</v>
+        <v>2.272000074386597</v>
       </c>
       <c r="I52" t="n">
-        <v>5.315614634781944</v>
+        <v>4.57746463886355</v>
       </c>
       <c r="J52" t="n">
-        <v>-4</v>
+        <v>-25</v>
       </c>
       <c r="K52" t="n">
-        <v>-2</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.025</v>
+        <v>0.29</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2916,30 +2916,30 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>IT0005433765</t>
+          <t>IT0004056880</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8550000190734863</v>
+        <v>10.64999961853027</v>
       </c>
       <c r="I53" t="n">
-        <v>2.923976542958566</v>
+        <v>2.723004792370318</v>
       </c>
       <c r="J53" t="n">
-        <v>-4</v>
+        <v>-25</v>
       </c>
       <c r="K53" t="n">
-        <v>-2</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2948,45 +2948,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>NL0015000K93</t>
+          <t>IT0000062072</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.89999961853027</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="I54" t="n">
-        <v>3.978494678052877</v>
+        <v>3.983483295943059</v>
       </c>
       <c r="J54" t="n">
-        <v>-8</v>
+        <v>-25</v>
       </c>
       <c r="K54" t="n">
-        <v>20</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.03</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3010,30 +3010,30 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>IT0001237053</t>
+          <t>IT0003261697</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.878000020980835</v>
+        <v>36.72000122070312</v>
       </c>
       <c r="I55" t="n">
-        <v>3.416856410377562</v>
+        <v>5.44662291261684</v>
       </c>
       <c r="J55" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="K55" t="n">
-        <v>-9</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.023</v>
+        <v>0.1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3057,30 +3057,30 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>IT0000060886</t>
+          <t>NL0015000N33</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4810000061988831</v>
+        <v>3.220000028610229</v>
       </c>
       <c r="I56" t="n">
-        <v>4.781704720080606</v>
+        <v>3.105590034518123</v>
       </c>
       <c r="J56" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="K56" t="n">
-        <v>-9</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6</v>
+        <v>0.14846</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3104,30 +3104,30 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>IT0005245508</t>
+          <t>IT0005119810</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.10000038146973</v>
+        <v>37.40999984741211</v>
       </c>
       <c r="I57" t="n">
-        <v>3.141361193804492</v>
+        <v>0.3968457647835835</v>
       </c>
       <c r="J57" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="K57" t="n">
-        <v>-9</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3151,30 +3151,30 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>IT0005469264</t>
+          <t>IT0003188064</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.539999961853027</v>
+        <v>21.34000015258789</v>
       </c>
       <c r="I58" t="n">
-        <v>2.096436067083091</v>
+        <v>4.311152733934878</v>
       </c>
       <c r="J58" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="K58" t="n">
-        <v>-9</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3198,30 +3198,30 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>IT0004329733</t>
+          <t>NL0015001KT6</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.5</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="I59" t="n">
-        <v>7.199999999999999</v>
+        <v>2.692998121672573</v>
       </c>
       <c r="J59" t="n">
-        <v>-18</v>
+        <v>-25</v>
       </c>
       <c r="K59" t="n">
-        <v>-16</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3</v>
+        <v>1.04</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3245,30 +3245,30 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>IT0005600249</t>
+          <t>IT0004764699</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.25</v>
+        <v>85.41999816894531</v>
       </c>
       <c r="I60" t="n">
-        <v>3.636363636363636</v>
+        <v>1.217513488987752</v>
       </c>
       <c r="J60" t="n">
-        <v>-18</v>
+        <v>-25</v>
       </c>
       <c r="K60" t="n">
-        <v>-16</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3277,12 +3277,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3292,30 +3292,30 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>IT0005453250</t>
+          <t>IT0001347308</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16.85000038146973</v>
+        <v>46.18999862670898</v>
       </c>
       <c r="I61" t="n">
-        <v>1.483679491633305</v>
+        <v>1.515479586083449</v>
       </c>
       <c r="J61" t="n">
-        <v>-18</v>
+        <v>-25</v>
       </c>
       <c r="K61" t="n">
-        <v>-16</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.03</v>
+        <v>0.86</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3339,30 +3339,30 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>IT0005588626</t>
+          <t>IT0005508921</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.940000057220459</v>
+        <v>10.71599960327148</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7614213087388637</v>
+        <v>8.025382902566092</v>
       </c>
       <c r="J62" t="n">
-        <v>-18</v>
+        <v>-25</v>
       </c>
       <c r="K62" t="n">
-        <v>-16</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3386,30 +3386,30 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>IT0005275778</t>
+          <t>IT0000066123</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.170000076293945</v>
+        <v>13.04399967193604</v>
       </c>
       <c r="I63" t="n">
-        <v>3.597122236345648</v>
+        <v>4.2931617148445</v>
       </c>
       <c r="J63" t="n">
-        <v>-18</v>
+        <v>-25</v>
       </c>
       <c r="K63" t="n">
-        <v>-16</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.58</v>
+        <v>0.04</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3433,30 +3433,30 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>IT0001042610</t>
+          <t>IT0001472171</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.64999961853027</v>
+        <v>2.410000085830688</v>
       </c>
       <c r="I64" t="n">
-        <v>4.584980375417487</v>
+        <v>1.659750978233374</v>
       </c>
       <c r="J64" t="n">
-        <v>-18</v>
+        <v>-25</v>
       </c>
       <c r="K64" t="n">
-        <v>-16</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.104</v>
+        <v>0.3</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>IT0001233417</t>
+          <t>IT0003127930</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.275000095367432</v>
+        <v>9.520000457763672</v>
       </c>
       <c r="I65" t="n">
-        <v>4.571428379795436</v>
+        <v>3.151260352675157</v>
       </c>
       <c r="J65" t="n">
         <v>-25</v>
@@ -3499,11 +3499,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.29</v>
+        <v>0.108</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3527,14 +3527,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>IT0004056880</t>
+          <t>IT0005244618</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.52999973297119</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I66" t="n">
-        <v>2.754036157208641</v>
+        <v>4.954128288658833</v>
       </c>
       <c r="J66" t="n">
         <v>-25</v>
@@ -3546,11 +3546,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.077</v>
+        <v>2.06</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3569,19 +3569,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>IT0001469383</t>
+          <t>IT0001128047</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.095000028610229</v>
+        <v>92.80000305175781</v>
       </c>
       <c r="I67" t="n">
-        <v>3.675417610904753</v>
+        <v>2.219827513207156</v>
       </c>
       <c r="J67" t="n">
         <v>-25</v>
@@ -3593,11 +3593,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.64</v>
+        <v>0.75</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>IT0000062072</t>
+          <t>IT0003121677</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>41.33000183105469</v>
+        <v>16.45999908447266</v>
       </c>
       <c r="I68" t="n">
-        <v>3.968061764680907</v>
+        <v>4.556500860972122</v>
       </c>
       <c r="J68" t="n">
         <v>-25</v>
@@ -3640,11 +3640,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>IT0003261697</t>
+          <t>NL0013995087</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>36.5099983215332</v>
+        <v>15.47000026702881</v>
       </c>
       <c r="I69" t="n">
-        <v>5.477951498070658</v>
+        <v>1.939237199881564</v>
       </c>
       <c r="J69" t="n">
         <v>-25</v>
@@ -3687,11 +3687,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.1</v>
+        <v>0.85</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3715,14 +3715,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>NL0015000N33</t>
+          <t>IT0005246191</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.230000019073486</v>
+        <v>49.5</v>
       </c>
       <c r="I70" t="n">
-        <v>3.095975213916087</v>
+        <v>1.717171717171717</v>
       </c>
       <c r="J70" t="n">
         <v>-25</v>
@@ -3734,11 +3734,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.14846</v>
+        <v>0.85</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3762,14 +3762,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>IT0005119810</t>
+          <t>IT0003115950</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>40.18000030517578</v>
+        <v>37.29999923706055</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3694873043116332</v>
+        <v>2.278820421946435</v>
       </c>
       <c r="J71" t="n">
         <v>-25</v>
@@ -3781,11 +3781,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.92</v>
+        <v>1.3</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3809,14 +3809,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>IT0003188064</t>
+          <t>IT0003492391</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>21.44000053405762</v>
+        <v>66.5</v>
       </c>
       <c r="I72" t="n">
-        <v>4.291044669232039</v>
+        <v>1.954887218045113</v>
       </c>
       <c r="J72" t="n">
         <v>-25</v>
@@ -3828,11 +3828,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>NL0015001KT6</t>
+          <t>IT0001463063</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.26000022888184</v>
+        <v>7.039999961853027</v>
       </c>
       <c r="I73" t="n">
-        <v>2.66429834726381</v>
+        <v>8.522727318908558</v>
       </c>
       <c r="J73" t="n">
         <v>-25</v>
@@ -3875,11 +3875,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.04</v>
+        <v>0.47</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>IT0004764699</t>
+          <t>IT0005669558</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>87.76000213623047</v>
+        <v>6.5</v>
       </c>
       <c r="I74" t="n">
-        <v>1.185050107890381</v>
+        <v>7.230769230769231</v>
       </c>
       <c r="J74" t="n">
         <v>-25</v>
@@ -3922,11 +3922,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>IT0001347308</t>
+          <t>IT0001157020</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>46.4900016784668</v>
+        <v>24.05999946594238</v>
       </c>
       <c r="I75" t="n">
-        <v>1.505700096208483</v>
+        <v>4.156276068981334</v>
       </c>
       <c r="J75" t="n">
         <v>-25</v>
@@ -3969,11 +3969,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.2</v>
+        <v>0.215</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3992,19 +3992,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>IT0001031084</t>
+          <t>IT0004356751</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>59.84999847412109</v>
+        <v>4.920000076293945</v>
       </c>
       <c r="I76" t="n">
-        <v>3.675856401151408</v>
+        <v>4.369918631423103</v>
       </c>
       <c r="J76" t="n">
         <v>-25</v>
@@ -4016,11 +4016,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.86</v>
+        <v>0.2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4044,14 +4044,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>IT0005508921</t>
+          <t>IT0005521247</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10.69999980926514</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="I77" t="n">
-        <v>8.037383320841981</v>
+        <v>2.040816286810733</v>
       </c>
       <c r="J77" t="n">
         <v>-25</v>
@@ -4063,11 +4063,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4091,14 +4091,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>IT0000066123</t>
+          <t>IT0004967292</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>13.03600025177002</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I78" t="n">
-        <v>4.295796173553799</v>
+        <v>2.614378998056083</v>
       </c>
       <c r="J78" t="n">
         <v>-25</v>
@@ -4110,11 +4110,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.04</v>
+        <v>0.79</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4138,14 +4138,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IT0001472171</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.380000114440918</v>
+        <v>21.93000030517578</v>
       </c>
       <c r="I79" t="n">
-        <v>1.680672188093417</v>
+        <v>3.6023711309003</v>
       </c>
       <c r="J79" t="n">
         <v>-25</v>
@@ -4157,11 +4157,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.3</v>
+        <v>0.093</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>IT0003127930</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>9.649999618530273</v>
+        <v>5.360000133514404</v>
       </c>
       <c r="I80" t="n">
-        <v>3.108808413048321</v>
+        <v>1.735074583645998</v>
       </c>
       <c r="J80" t="n">
         <v>-25</v>
@@ -4204,11 +4204,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.108</v>
+        <v>0.06</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4227,19 +4227,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>IT0005244618</t>
+          <t>IT0005359101</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.190000057220459</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I81" t="n">
-        <v>4.931506720464348</v>
+        <v>0.8108108003614941</v>
       </c>
       <c r="J81" t="n">
         <v>-25</v>
@@ -4251,11 +4251,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.06</v>
+        <v>0.35</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4279,14 +4279,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>IT0001128047</t>
+          <t>IT0001078911</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>92.30000305175781</v>
+        <v>35</v>
       </c>
       <c r="I82" t="n">
-        <v>2.231852580595086</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>-25</v>
@@ -4298,11 +4298,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.75</v>
+        <v>0.5543</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4326,14 +4326,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>IT0003121677</t>
+          <t>IT0005090300</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>16.21999931335449</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="I83" t="n">
-        <v>4.623921280825819</v>
+        <v>8.424012255729656</v>
       </c>
       <c r="J83" t="n">
         <v>-25</v>
@@ -4345,11 +4345,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4373,14 +4373,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>NL0013995087</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>15.65999984741211</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I84" t="n">
-        <v>1.915708830926818</v>
+        <v>2.678571417167479</v>
       </c>
       <c r="J84" t="n">
         <v>-25</v>
@@ -4392,11 +4392,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4420,14 +4420,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>IT0005246191</t>
+          <t>IT0003411417</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>51</v>
+        <v>14.19999980926514</v>
       </c>
       <c r="I85" t="n">
-        <v>1.666666666666667</v>
+        <v>1.408450723143708</v>
       </c>
       <c r="J85" t="n">
         <v>-25</v>
@@ -4439,11 +4439,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.85</v>
+        <v>0.103</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4467,14 +4467,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>IT0003115950</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>37.22000122070312</v>
+        <v>7.164999961853027</v>
       </c>
       <c r="I86" t="n">
-        <v>2.283718356052065</v>
+        <v>1.437543622447723</v>
       </c>
       <c r="J86" t="n">
         <v>-25</v>
@@ -4486,11 +4486,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.3</v>
+        <v>0.19</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4514,14 +4514,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IT0003492391</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>68.59999847412109</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I87" t="n">
-        <v>1.895043773930136</v>
+        <v>3.253424572528563</v>
       </c>
       <c r="J87" t="n">
         <v>-25</v>
@@ -4533,11 +4533,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6</v>
+        <v>0.432</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4561,14 +4561,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>IT0001463063</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>7.179999828338623</v>
+        <v>10.64999961853027</v>
       </c>
       <c r="I88" t="n">
-        <v>8.356546160793345</v>
+        <v>4.056338173461992</v>
       </c>
       <c r="J88" t="n">
         <v>-25</v>
@@ -4580,11 +4580,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IT0005669558</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6.5</v>
+        <v>27.53000068664551</v>
       </c>
       <c r="I89" t="n">
-        <v>7.230769230769231</v>
+        <v>1.598256407648544</v>
       </c>
       <c r="J89" t="n">
         <v>-25</v>
@@ -4627,11 +4627,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4650,19 +4650,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IT0005312027</t>
+          <t>IT0004522162</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.71999979019165</v>
+        <v>1.039999961853027</v>
       </c>
       <c r="I90" t="n">
-        <v>3.496503624754485</v>
+        <v>2.88461549042245</v>
       </c>
       <c r="J90" t="n">
         <v>-25</v>
@@ -4674,11 +4674,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>0.47</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>IT0001157020</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>24.05999946594238</v>
+        <v>6.909999847412109</v>
       </c>
       <c r="I91" t="n">
-        <v>4.156276068981334</v>
+        <v>6.801736763800675</v>
       </c>
       <c r="J91" t="n">
         <v>-25</v>
@@ -4721,11 +4721,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.215</v>
+        <v>1.4</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4749,14 +4749,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>IT0004356751</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4.920000076293945</v>
+        <v>53.86000061035156</v>
       </c>
       <c r="I92" t="n">
-        <v>4.369918631423103</v>
+        <v>2.59933157098949</v>
       </c>
       <c r="J92" t="n">
         <v>-25</v>
@@ -4768,11 +4768,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4791,19 +4791,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>22.85000038146973</v>
+        <v>3.394999980926514</v>
       </c>
       <c r="I93" t="n">
-        <v>1.181619236290942</v>
+        <v>8.836524350086398</v>
       </c>
       <c r="J93" t="n">
         <v>-25</v>
@@ -4815,11 +4815,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IT0005521247</t>
+          <t>IT0005594418</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9.920000076293945</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="I94" t="n">
-        <v>2.016129016752174</v>
+        <v>0.7643312194767268</v>
       </c>
       <c r="J94" t="n">
         <v>-25</v>
@@ -4862,11 +4862,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>IT0004967292</t>
+          <t>IT0005453748</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>9.154999732971191</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I95" t="n">
-        <v>2.621518372476344</v>
+        <v>5.151515225952543</v>
       </c>
       <c r="J95" t="n">
         <v>-25</v>
@@ -4909,11 +4909,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IT0000072170</t>
+          <t>IT0005373789</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>22.01000022888184</v>
+        <v>22.64999961853027</v>
       </c>
       <c r="I96" t="n">
-        <v>3.589277563765542</v>
+        <v>3.090507778319433</v>
       </c>
       <c r="J96" t="n">
         <v>-25</v>
@@ -4956,11 +4956,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.093</v>
+        <v>0.035</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4984,14 +4984,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>IT0005345233</t>
+          <t>IT0005378143</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.340000152587891</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="I97" t="n">
-        <v>1.741572983943268</v>
+        <v>1.22377626866407</v>
       </c>
       <c r="J97" t="n">
         <v>-25</v>
@@ -5003,11 +5003,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5026,19 +5026,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>IT0005359101</t>
+          <t>IT0005054967</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7.400000095367432</v>
+        <v>5.610000133514404</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8108108003614941</v>
+        <v>5.882352801180245</v>
       </c>
       <c r="J98" t="n">
         <v>-25</v>
@@ -5050,11 +5050,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5078,14 +5078,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IT0001078911</t>
+          <t>IT0004931496</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>34.81999969482422</v>
+        <v>0.9430000185966492</v>
       </c>
       <c r="I99" t="n">
-        <v>1.005169451658626</v>
+        <v>7.423117563048661</v>
       </c>
       <c r="J99" t="n">
         <v>-25</v>
@@ -5097,11 +5097,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5543</v>
+        <v>0.71</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IT0005090300</t>
+          <t>IT0003828271</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.625</v>
+        <v>50.79999923706055</v>
       </c>
       <c r="I100" t="n">
-        <v>8.36679245283019</v>
+        <v>1.397637816266004</v>
       </c>
       <c r="J100" t="n">
         <v>-25</v>
@@ -5144,11 +5144,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.06</v>
+        <v>1.35</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IT0001077780</t>
+          <t>IT0005282865</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.25</v>
+        <v>100.1999969482422</v>
       </c>
       <c r="I101" t="n">
-        <v>2.666666666666667</v>
+        <v>1.347305430255987</v>
       </c>
       <c r="J101" t="n">
         <v>-25</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0003411417</t>
+          <t>IT0005543613</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>14.35000038146973</v>
+        <v>7.320000171661377</v>
       </c>
       <c r="I102" t="n">
-        <v>1.393728185946682</v>
+        <v>1.092896149233872</v>
       </c>
       <c r="J102" t="n">
         <v>-25</v>
@@ -5238,11 +5238,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.103</v>
+        <v>3</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005186371</t>
+          <t>IT0001017851</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.130000114440918</v>
+        <v>254</v>
       </c>
       <c r="I103" t="n">
-        <v>1.44460025731818</v>
+        <v>1.181102362204724</v>
       </c>
       <c r="J103" t="n">
         <v>-25</v>
@@ -5285,11 +5285,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0000072618</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.806000232696533</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="I104" t="n">
-        <v>3.272476617035142</v>
+        <v>3.601695075352903</v>
       </c>
       <c r="J104" t="n">
         <v>-25</v>
@@ -5332,11 +5332,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.432</v>
+        <v>0.297</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.64000034332275</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I105" t="n">
-        <v>4.060150244930266</v>
+        <v>4.013513461789396</v>
       </c>
       <c r="J105" t="n">
         <v>-25</v>
@@ -5379,11 +5379,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5407,14 +5407,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>27.86000061035156</v>
+        <v>61</v>
       </c>
       <c r="I106" t="n">
-        <v>1.579325162816096</v>
+        <v>0.7377049180327869</v>
       </c>
       <c r="J106" t="n">
         <v>-25</v>
@@ -5426,11 +5426,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0004522162</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>1.039999961853027</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="I107" t="n">
-        <v>2.88461549042245</v>
+        <v>0.709219874945225</v>
       </c>
       <c r="J107" t="n">
         <v>-25</v>
@@ -5473,11 +5473,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7.039999961853027</v>
+        <v>37.22000122070312</v>
       </c>
       <c r="I108" t="n">
-        <v>6.676136399811703</v>
+        <v>2.821063851593728</v>
       </c>
       <c r="J108" t="n">
         <v>-25</v>
@@ -5520,11 +5520,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.4</v>
+        <v>0.05</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>56.88000106811523</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="I109" t="n">
-        <v>2.461322035355563</v>
+        <v>3.225806550850609</v>
       </c>
       <c r="J109" t="n">
         <v>-25</v>
@@ -5567,11 +5567,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.433000087738037</v>
+        <v>16.80999946594238</v>
       </c>
       <c r="I110" t="n">
-        <v>8.73871227302142</v>
+        <v>2.260559262776258</v>
       </c>
       <c r="J110" t="n">
         <v>-25</v>
@@ -5614,15 +5614,15 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5642,14 +5642,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>16</v>
+        <v>27.1200008392334</v>
       </c>
       <c r="I111" t="n">
-        <v>0.75</v>
+        <v>2.212389312068178</v>
       </c>
       <c r="J111" t="n">
         <v>-25</v>
@@ -5661,11 +5661,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.349999904632568</v>
+        <v>36.84999847412109</v>
       </c>
       <c r="I112" t="n">
-        <v>5.074627010135566</v>
+        <v>0.9497965115135539</v>
       </c>
       <c r="J112" t="n">
         <v>-25</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7</v>
+        <v>0.017</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0005373789</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>22.60000038146973</v>
+        <v>3.359999895095825</v>
       </c>
       <c r="I113" t="n">
-        <v>3.097345080462682</v>
+        <v>0.505952396748964</v>
       </c>
       <c r="J113" t="n">
         <v>-25</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.035</v>
+        <v>0.01</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5783,14 +5783,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.900000095367432</v>
+        <v>2.825000047683716</v>
       </c>
       <c r="I114" t="n">
-        <v>1.206896512034959</v>
+        <v>0.3539822949100208</v>
       </c>
       <c r="J114" t="n">
         <v>-25</v>
@@ -5802,11 +5802,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.33</v>
+        <v>1.12</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.590000152587891</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="I115" t="n">
-        <v>5.903398765512136</v>
+        <v>4.628099027646309</v>
       </c>
       <c r="J115" t="n">
         <v>-25</v>
@@ -5849,11 +5849,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9520000219345093</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I116" t="n">
-        <v>7.352941007055512</v>
+        <v>7.518796749870864</v>
       </c>
       <c r="J116" t="n">
         <v>-25</v>
@@ -5896,11 +5896,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.71</v>
+        <v>0.26</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5924,865 +5924,19 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>IT0003828271</t>
+          <t>IT0003865588</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>50.84999847412109</v>
+        <v>9.279999732971191</v>
       </c>
       <c r="I117" t="n">
-        <v>1.396263562055637</v>
+        <v>2.801724218549686</v>
       </c>
       <c r="J117" t="n">
         <v>-25</v>
       </c>
       <c r="K117" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>REPLY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>IT0005282865</t>
-        </is>
-      </c>
-      <c r="H118" t="n">
-        <v>99.80000305175781</v>
-      </c>
-      <c r="I118" t="n">
-        <v>1.352705369457624</v>
-      </c>
-      <c r="J118" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K118" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>RES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>IT0005543613</t>
-        </is>
-      </c>
-      <c r="H119" t="n">
-        <v>7.320000171661377</v>
-      </c>
-      <c r="I119" t="n">
-        <v>1.092896149233872</v>
-      </c>
-      <c r="J119" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K119" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>ROSETTI MARINO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>3</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>IT0001017851</t>
-        </is>
-      </c>
-      <c r="H120" t="n">
-        <v>254</v>
-      </c>
-      <c r="I120" t="n">
-        <v>1.181102362204724</v>
-      </c>
-      <c r="J120" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K120" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>SAIPEM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>IT0005495657</t>
-        </is>
-      </c>
-      <c r="H121" t="n">
-        <v>4.629000186920166</v>
-      </c>
-      <c r="I121" t="n">
-        <v>3.672499311630119</v>
-      </c>
-      <c r="J121" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K121" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>SBE-Varvit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>IT0005568461</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
-        <v>7.400000095367432</v>
-      </c>
-      <c r="I122" t="n">
-        <v>4.013513461789396</v>
-      </c>
-      <c r="J122" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K122" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>SOL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>IT0001206769</t>
-        </is>
-      </c>
-      <c r="H123" t="n">
-        <v>61.20000076293945</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0.7352941084806391</v>
-      </c>
-      <c r="J123" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K123" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>SYS-DAT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>IT0005595423</t>
-        </is>
-      </c>
-      <c r="H124" t="n">
-        <v>5.739999771118164</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0.6968641392856347</v>
-      </c>
-      <c r="J124" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K124" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>IT0003549422</t>
-        </is>
-      </c>
-      <c r="H125" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="I125" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J125" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K125" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Smart Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>IT0005621070</t>
-        </is>
-      </c>
-      <c r="H126" t="n">
-        <v>1.549999952316284</v>
-      </c>
-      <c r="I126" t="n">
-        <v>3.225806550850609</v>
-      </c>
-      <c r="J126" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K126" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>TECHNOGYM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>IT0005162406</t>
-        </is>
-      </c>
-      <c r="H127" t="n">
-        <v>16.63999938964844</v>
-      </c>
-      <c r="I127" t="n">
-        <v>2.283653929917773</v>
-      </c>
-      <c r="J127" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K127" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>TENARIS S.A.</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>LU2598331598</t>
-        </is>
-      </c>
-      <c r="H128" t="n">
-        <v>26.6200008392334</v>
-      </c>
-      <c r="I128" t="n">
-        <v>2.253944331645929</v>
-      </c>
-      <c r="J128" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K128" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>IT0001454435</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
-        <v>37.04999923706055</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0.9446693851747784</v>
-      </c>
-      <c r="J129" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K129" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>IT0005658841</t>
-        </is>
-      </c>
-      <c r="H130" t="n">
-        <v>3.319999933242798</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0.5120482030671402</v>
-      </c>
-      <c r="J130" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K130" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>IT0005573065</t>
-        </is>
-      </c>
-      <c r="H131" t="n">
-        <v>2.835000038146973</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0.352733681320733</v>
-      </c>
-      <c r="J131" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K131" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>IT0004810054</t>
-        </is>
-      </c>
-      <c r="H132" t="n">
-        <v>24.13999938964844</v>
-      </c>
-      <c r="I132" t="n">
-        <v>4.639602437108062</v>
-      </c>
-      <c r="J132" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K132" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>IT0004717200</t>
-        </is>
-      </c>
-      <c r="H133" t="n">
-        <v>1.309999942779541</v>
-      </c>
-      <c r="I133" t="n">
-        <v>7.633588119692685</v>
-      </c>
-      <c r="J133" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K133" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>WEBUILD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>IT0003865588</t>
-        </is>
-      </c>
-      <c r="H134" t="n">
-        <v>9.380000114440918</v>
-      </c>
-      <c r="I134" t="n">
-        <v>2.771854976842897</v>
-      </c>
-      <c r="J134" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K134" t="n">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>doValue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>0.09229999999999999</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>IT0005610958</t>
-        </is>
-      </c>
-      <c r="H135" t="n">
-        <v>2.335999965667725</v>
-      </c>
-      <c r="I135" t="n">
-        <v>3.951198688207894</v>
-      </c>
-      <c r="J135" t="n">
-        <v>-25</v>
-      </c>
-      <c r="K135" t="n">
         <v>-23</v>
       </c>
     </row>
@@ -8575,112 +7729,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>E-NOVIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Predict S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Tenax International S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tenax International S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>doxee S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>